--- a/jpcore-r4/develop/ValueSet-jp-documentcodes-endoscopy-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-documentcodes-endoscopy-vs.xlsx
@@ -93,7 +93,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright JED-Project 一般社団法人 日本消化器内視鏡学会</t>
+    <t>Copyright JED-Project 一般社団法人 日本消化器内視鏡学会  
+Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>Immutable</t>
